--- a/analysis/tables/bloom-560m.xlsx
+++ b/analysis/tables/bloom-560m.xlsx
@@ -536,27 +536,27 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.5990826765635748</v>
+        <v>0.4832600257612836</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1451049396052904</v>
+        <v>-0.1171477480323237</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>y = 0.599x - 0.145</t>
+          <t>y = 0.483x - 0.117</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.5885366722060511</v>
+        <v>0.5885366722060508</v>
       </c>
       <c r="H3" t="n">
         <v>0.07729454616211583</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2422118770611652</v>
+        <v>0.2424114178444199</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4539777369582845</v>
+        <v>0.3661122777289599</v>
       </c>
       <c r="K3" t="n">
         <v>0.09729531263741434</v>
@@ -577,27 +577,27 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.6693714833209766</v>
+        <v>0.4789549017409616</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02322502367856069</v>
+        <v>-0.1103914231048476</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>y = 0.669x + 0.023</t>
+          <t>y = 0.479x - 0.110</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.624070185767616</v>
+        <v>0.5914468785146928</v>
       </c>
       <c r="H4" t="n">
-        <v>0.07651912608680006</v>
+        <v>0.07723103900594563</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.03469676294444686</v>
+        <v>0.2304839614410122</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6925965069995373</v>
+        <v>0.3685634786361139</v>
       </c>
       <c r="K4" t="n">
         <v>0.09729531263741434</v>
